--- a/results/Int Task Remove ACC -0.8/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_7_permute.xlsx
@@ -440,187 +440,187 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6377464053711792</v>
+        <v>0.6524146700015474</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6415869658585265</v>
+        <v>0.6524146700015474</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6471044408232356</v>
+        <v>0.6459714971909314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6478106555125011</v>
+        <v>0.639794191117722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6417042077605455</v>
+        <v>0.6434138868098518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.637334677075537</v>
+        <v>0.6445604494509762</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.637334677075537</v>
+        <v>0.6496948157762599</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.638424000404228</v>
+        <v>0.6298171815836262</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6312446116095537</v>
+        <v>0.6485904918001724</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6313618535115726</v>
+        <v>0.6514644974151516</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.633510498874162</v>
+        <v>0.6411971464031605</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6308901226263449</v>
+        <v>0.6471263496635118</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6299780437892583</v>
+        <v>0.6378460807255892</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6165885843494299</v>
+        <v>0.6378460807255892</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6162354770047971</v>
+        <v>0.6245616258175353</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6162504776521934</v>
+        <v>0.6251369795959615</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6611728769346887</v>
+        <v>0.625195600546971</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6587897477680615</v>
+        <v>0.6210319340097836</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6437561384228161</v>
+        <v>0.6161034318323212</v>
       </c>
     </row>
     <row r="21">
@@ -630,697 +630,697 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6470527280651059</v>
+        <v>0.6598287399771989</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6602049404237447</v>
+        <v>0.641749407079674</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6832891603742899</v>
+        <v>0.6350839878352645</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6808037899530401</v>
+        <v>0.6299182385766122</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6798617098211607</v>
+        <v>0.6819914069975652</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6635410054539196</v>
+        <v>0.6865395638127541</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6327375707793705</v>
+        <v>0.6905982258181669</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6321785992869167</v>
+        <v>0.7090592857165414</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6327811910829836</v>
+        <v>0.7081472068794548</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6483615345504385</v>
+        <v>0.7081472068794548</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6325277590927608</v>
+        <v>0.6911271960158281</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6408550921671357</v>
+        <v>0.6818155441445367</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6271152886598264</v>
+        <v>0.6530135116357654</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6210266048324191</v>
+        <v>0.6583265040912292</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6098716497238301</v>
+        <v>0.6546945710288549</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6032348501356375</v>
+        <v>0.6537088705933625</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5941890650017527</v>
+        <v>0.6537088705933625</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6099519821381765</v>
+        <v>0.6752892756424225</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5838275651896556</v>
+        <v>0.6702571505717615</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5888583086217405</v>
+        <v>0.6654022699927049</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5809154658253672</v>
+        <v>0.6592535835757123</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.558972479338582</v>
+        <v>0.6636912093048226</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.554870197029556</v>
+        <v>0.6639870773370219</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5697565631779898</v>
+        <v>0.6639870773370219</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5624599324812966</v>
+        <v>0.6483522578342855</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5794471787729786</v>
+        <v>0.6320970826109338</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5763686906487543</v>
+        <v>0.6482772545973037</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.594314399358288</v>
+        <v>0.6410106251954032</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6018318948501988</v>
+        <v>0.6381571467821243</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6340327582558827</v>
+        <v>0.6344638294915885</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6528496887760419</v>
+        <v>0.6170620916271123</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6644982836101347</v>
+        <v>0.6075323382377555</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6443822180746748</v>
+        <v>0.5857188310232336</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6338531452410051</v>
+        <v>0.5780771854364241</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.568955212803921</v>
+        <v>0.5661315383084955</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5648365482089227</v>
+        <v>0.5822939463703171</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5645570624626958</v>
+        <v>0.5697920910270864</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5475384332376451</v>
+        <v>0.580991850700925</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5234140368163257</v>
+        <v>0.6101185682750518</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5330624137462775</v>
+        <v>0.6103189058685691</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5038977997997808</v>
+        <v>0.5909021468294948</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.511428914300512</v>
+        <v>0.6317943063858545</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5110758069558792</v>
+        <v>0.6381310930261201</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5152680931492833</v>
+        <v>0.6079588698038547</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5167377618402479</v>
+        <v>0.6013356892244823</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5181638102275993</v>
+        <v>0.5964235693329922</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5188414052606481</v>
+        <v>0.5940240578803928</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5187827843096386</v>
+        <v>0.6085314603051289</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5241816357337526</v>
+        <v>0.6139016920730263</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5241816357337526</v>
+        <v>0.6097473022519919</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5222402361575604</v>
+        <v>0.5882515719099456</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5217398856161161</v>
+        <v>0.5750202113985972</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5115461562025309</v>
+        <v>0.6027398287715575</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5115461562025309</v>
+        <v>0.6394069375625685</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5145754974688381</v>
+        <v>0.6292513018982924</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5066776566146539</v>
+        <v>0.5665487931584415</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5082809494936097</v>
+        <v>0.5322563263256626</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5024267494702404</v>
+        <v>0.5319032189810298</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5024267494702404</v>
+        <v>0.5308152772909146</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4974096250469757</v>
+        <v>0.5227699958629793</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4986161902776857</v>
+        <v>0.5579388163068091</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4986161902776857</v>
+        <v>0.530227686142244</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4986161902776857</v>
+        <v>0.5601831894850199</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5013224254941528</v>
+        <v>0.5601831894850199</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4999099961156219</v>
+        <v>0.5599037037387929</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4999099961156219</v>
+        <v>0.5644054769732167</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4975554866052114</v>
+        <v>0.539899353551048</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4948778710449609</v>
+        <v>0.5364419017031261</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4973496224573902</v>
+        <v>0.5146378685816967</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4973496224573902</v>
+        <v>0.5037298320243295</v>
       </c>
     </row>
   </sheetData>
